--- a/uploads/excel_format/uzhavan bulkupload format.xlsx
+++ b/uploads/excel_format/uzhavan bulkupload format.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="126">
   <si>
     <t>cus_name</t>
   </si>
@@ -324,9 +324,6 @@
     <t>State Bank of India</t>
   </si>
   <si>
-    <t>sri</t>
-  </si>
-  <si>
     <t>Teacher</t>
   </si>
   <si>
@@ -336,12 +333,6 @@
     <t>villainur</t>
   </si>
   <si>
-    <t>thenu</t>
-  </si>
-  <si>
-    <t>Mani</t>
-  </si>
-  <si>
     <t>lakshmi</t>
   </si>
   <si>
@@ -376,6 +367,33 @@
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>L3</t>
+  </si>
+  <si>
+    <t>collection_method</t>
+  </si>
+  <si>
+    <t>Byself</t>
+  </si>
+  <si>
+    <t>On Spot</t>
+  </si>
+  <si>
+    <t>Maya</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Riyaz</t>
+  </si>
+  <si>
+    <t>srilaksmi</t>
+  </si>
+  <si>
+    <t>Logeswaari</t>
   </si>
 </sst>
 </file>
@@ -760,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BZ29"/>
+  <dimension ref="A1:CA29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
@@ -820,24 +838,25 @@
     <col min="59" max="59" width="16.140625" customWidth="1"/>
     <col min="60" max="60" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="13.5703125" customWidth="1"/>
-    <col min="62" max="62" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="12" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="12" customWidth="1"/>
-    <col min="66" max="66" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="15.140625" customWidth="1"/>
-    <col min="68" max="68" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="69" max="70" width="13.5703125" customWidth="1"/>
-    <col min="71" max="71" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="12" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="19" customWidth="1"/>
-    <col min="74" max="75" width="12" customWidth="1"/>
-    <col min="76" max="76" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="20.5703125" customWidth="1"/>
+    <col min="63" max="63" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="12" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="12" customWidth="1"/>
+    <col min="67" max="67" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="15.140625" customWidth="1"/>
+    <col min="69" max="69" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="70" max="71" width="13.5703125" customWidth="1"/>
+    <col min="72" max="72" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="12" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="19" customWidth="1"/>
+    <col min="75" max="76" width="12" customWidth="1"/>
+    <col min="77" max="77" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:78" ht="15.75" thickBot="1">
+    <row r="1" spans="1:79" ht="15.75" thickBot="1">
       <c r="A1" t="s">
         <v>54</v>
       </c>
@@ -1022,69 +1041,72 @@
         <v>59</v>
       </c>
       <c r="BJ1" t="s">
+        <v>118</v>
+      </c>
+      <c r="BK1" t="s">
         <v>45</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>46</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>47</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>65</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>48</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>67</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>66</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BT1" t="s">
         <v>49</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BU1" t="s">
         <v>50</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BV1" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BW1" t="s">
         <v>70</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BX1" t="s">
         <v>71</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BY1" t="s">
         <v>51</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="BZ1" t="s">
         <v>52</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CA1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:78" ht="15.75" thickBot="1">
+    <row r="2" spans="1:79" ht="15.75" thickBot="1">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>100120013001</v>
+        <v>666655554444</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2">
@@ -1097,40 +1119,43 @@
         <v>55</v>
       </c>
       <c r="J2" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="K2" t="s">
         <v>75</v>
       </c>
       <c r="L2" s="1">
-        <v>589432889251</v>
+        <v>989432889251</v>
       </c>
       <c r="M2">
         <v>8798798790</v>
       </c>
       <c r="Q2" t="s">
+        <v>106</v>
+      </c>
+      <c r="R2" t="s">
+        <v>107</v>
+      </c>
+      <c r="S2" t="s">
+        <v>107</v>
+      </c>
+      <c r="T2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y2" t="s">
         <v>109</v>
       </c>
-      <c r="R2" t="s">
+      <c r="Z2" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="S2" t="s">
-        <v>110</v>
-      </c>
-      <c r="T2" t="s">
-        <v>111</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>112</v>
-      </c>
-      <c r="Z2" s="3" t="s">
-        <v>113</v>
+      <c r="AA2" t="s">
+        <v>117</v>
       </c>
       <c r="AB2">
         <v>890000</v>
       </c>
       <c r="AC2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -1151,7 +1176,7 @@
         <v>10000</v>
       </c>
       <c r="AL2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="AM2" s="3" t="s">
         <v>88</v>
@@ -1160,13 +1185,13 @@
         <v>20000</v>
       </c>
       <c r="AO2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="AP2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="AQ2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="AR2" t="s">
         <v>89</v>
@@ -1214,41 +1239,44 @@
       <c r="BI2" s="2">
         <v>46141</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BJ2" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BK2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BN2" t="s">
         <v>73</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BO2" t="s">
         <v>63</v>
-      </c>
-      <c r="BO2">
-        <v>19200</v>
       </c>
       <c r="BP2">
         <v>19200</v>
       </c>
-      <c r="BS2" s="1"/>
-      <c r="BX2" s="2">
+      <c r="BQ2">
+        <v>19200</v>
+      </c>
+      <c r="BT2" s="1"/>
+      <c r="BY2" s="2">
         <v>45867</v>
       </c>
-      <c r="BY2" t="s">
-        <v>108</v>
-      </c>
       <c r="BZ2" t="s">
+        <v>105</v>
+      </c>
+      <c r="CA2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:78" ht="15.75" thickBot="1">
+    <row r="3" spans="1:79" ht="15.75" thickBot="1">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>100120031003</v>
+        <v>777788889999</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="D3" t="s">
         <v>78</v>
@@ -1266,16 +1294,16 @@
         <v>77</v>
       </c>
       <c r="J3" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="K3" t="s">
         <v>75</v>
       </c>
       <c r="L3" s="1">
-        <v>890989089098</v>
+        <v>790989089098</v>
       </c>
       <c r="M3">
-        <v>8798798798</v>
+        <v>8798798791</v>
       </c>
       <c r="N3">
         <v>76</v>
@@ -1287,16 +1315,16 @@
         <v>57</v>
       </c>
       <c r="U3" t="s">
+        <v>102</v>
+      </c>
+      <c r="V3" t="s">
         <v>103</v>
-      </c>
-      <c r="V3" t="s">
-        <v>104</v>
       </c>
       <c r="W3">
         <v>40000</v>
       </c>
       <c r="X3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Y3" t="s">
         <v>90</v>
@@ -1394,144 +1422,156 @@
       <c r="BI3" s="2">
         <v>45929</v>
       </c>
-      <c r="BJ3" t="s">
+      <c r="BJ3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BK3" t="s">
         <v>98</v>
       </c>
-      <c r="BK3" t="s">
+      <c r="BL3" t="s">
         <v>99</v>
       </c>
-      <c r="BL3" t="s">
+      <c r="BM3" t="s">
         <v>100</v>
       </c>
-      <c r="BM3" t="s">
+      <c r="BN3" t="s">
         <v>73</v>
       </c>
-      <c r="BN3" t="s">
+      <c r="BO3" t="s">
         <v>63</v>
       </c>
-      <c r="BO3">
+      <c r="BP3">
         <v>29600</v>
       </c>
-      <c r="BQ3">
+      <c r="BR3">
         <v>29600</v>
       </c>
-      <c r="BS3" s="1"/>
-      <c r="BT3">
+      <c r="BT3" s="1"/>
+      <c r="BU3">
         <v>9999999999</v>
       </c>
-      <c r="BU3" s="3" t="s">
+      <c r="BV3" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="BV3" t="s">
+      <c r="BW3" t="s">
         <v>94</v>
       </c>
-      <c r="BX3" s="2">
+      <c r="BY3" s="2">
         <v>45867</v>
       </c>
-      <c r="BY3" t="s">
+      <c r="BZ3" t="s">
         <v>76</v>
       </c>
-      <c r="BZ3" t="s">
+      <c r="CA3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:78">
+    <row r="4" spans="1:79">
       <c r="B4" s="1"/>
       <c r="E4" s="2"/>
       <c r="L4" s="1"/>
       <c r="BG4" s="2"/>
       <c r="BH4" s="2"/>
       <c r="BI4" s="2"/>
-      <c r="BX4" s="2"/>
-    </row>
-    <row r="5" spans="1:78">
+      <c r="BJ4" s="2"/>
+      <c r="BY4" s="2"/>
+    </row>
+    <row r="5" spans="1:79">
       <c r="B5" s="1"/>
       <c r="E5" s="2"/>
       <c r="L5" s="1"/>
       <c r="BG5" s="2"/>
       <c r="BH5" s="2"/>
       <c r="BI5" s="2"/>
-      <c r="BS5" s="1"/>
-      <c r="BX5" s="2"/>
-    </row>
-    <row r="6" spans="1:78">
+      <c r="BJ5" s="2"/>
+      <c r="BT5" s="1"/>
+      <c r="BY5" s="2"/>
+    </row>
+    <row r="6" spans="1:79">
       <c r="B6" s="1"/>
       <c r="E6" s="2"/>
       <c r="L6" s="1"/>
       <c r="BG6" s="2"/>
       <c r="BH6" s="2"/>
       <c r="BI6" s="2"/>
-      <c r="BS6" s="1"/>
-      <c r="BX6" s="2"/>
-    </row>
-    <row r="7" spans="1:78">
+      <c r="BJ6" s="2"/>
+      <c r="BT6" s="1"/>
+      <c r="BY6" s="2"/>
+    </row>
+    <row r="7" spans="1:79">
       <c r="B7" s="1"/>
       <c r="E7" s="2"/>
       <c r="L7" s="1"/>
       <c r="BG7" s="2"/>
       <c r="BH7" s="2"/>
       <c r="BI7" s="2"/>
-      <c r="BS7" s="1"/>
-      <c r="BX7" s="2"/>
-    </row>
-    <row r="8" spans="1:78">
+      <c r="BJ7" s="2"/>
+      <c r="BT7" s="1"/>
+      <c r="BY7" s="2"/>
+    </row>
+    <row r="8" spans="1:79">
       <c r="B8" s="1"/>
       <c r="E8" s="2"/>
       <c r="L8" s="1"/>
       <c r="BG8" s="2"/>
       <c r="BH8" s="2"/>
       <c r="BI8" s="2"/>
-      <c r="BS8" s="1"/>
-      <c r="BX8" s="2"/>
-    </row>
-    <row r="9" spans="1:78">
+      <c r="BJ8" s="2"/>
+      <c r="BT8" s="1"/>
+      <c r="BY8" s="2"/>
+    </row>
+    <row r="9" spans="1:79">
       <c r="B9" s="1"/>
       <c r="E9" s="2"/>
       <c r="L9" s="1"/>
       <c r="BG9" s="2"/>
       <c r="BH9" s="2"/>
       <c r="BI9" s="2"/>
-      <c r="BS9" s="1"/>
-      <c r="BX9" s="2"/>
-    </row>
-    <row r="10" spans="1:78">
+      <c r="BJ9" s="2"/>
+      <c r="BT9" s="1"/>
+      <c r="BY9" s="2"/>
+    </row>
+    <row r="10" spans="1:79">
       <c r="B10" s="1"/>
       <c r="E10" s="2"/>
       <c r="L10" s="1"/>
       <c r="BG10" s="2"/>
       <c r="BH10" s="2"/>
       <c r="BI10" s="2"/>
-      <c r="BS10" s="1"/>
-      <c r="BX10" s="2"/>
-    </row>
-    <row r="11" spans="1:78">
+      <c r="BJ10" s="2"/>
+      <c r="BT10" s="1"/>
+      <c r="BY10" s="2"/>
+    </row>
+    <row r="11" spans="1:79">
       <c r="B11" s="1"/>
       <c r="E11" s="2"/>
       <c r="L11" s="1"/>
       <c r="BG11" s="2"/>
       <c r="BH11" s="2"/>
       <c r="BI11" s="2"/>
-      <c r="BX11" s="2"/>
-    </row>
-    <row r="12" spans="1:78">
+      <c r="BJ11" s="2"/>
+      <c r="BY11" s="2"/>
+    </row>
+    <row r="12" spans="1:79">
       <c r="B12" s="1"/>
       <c r="E12" s="2"/>
       <c r="L12" s="1"/>
       <c r="BG12" s="2"/>
       <c r="BH12" s="2"/>
       <c r="BI12" s="2"/>
-      <c r="BX12" s="2"/>
-    </row>
-    <row r="13" spans="1:78">
+      <c r="BJ12" s="2"/>
+      <c r="BY12" s="2"/>
+    </row>
+    <row r="13" spans="1:79">
       <c r="B13" s="1"/>
     </row>
-    <row r="14" spans="1:78">
+    <row r="14" spans="1:79">
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="1:78">
+    <row r="15" spans="1:79">
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="1:78">
+    <row r="16" spans="1:79">
       <c r="B16" s="1"/>
     </row>
     <row r="17" spans="2:2">
